--- a/appium-tests/reports/dry_run_python_report.xlsx
+++ b/appium-tests/reports/dry_run_python_report.xlsx
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="E6" s="7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -699,7 +699,7 @@
         </is>
       </c>
       <c r="E7" s="8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -720,7 +720,7 @@
       </c>
       <c r="E8" s="9" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>100.0%</t>
         </is>
       </c>
     </row>
@@ -966,12 +966,12 @@
       </c>
       <c r="F4" s="14" t="inlineStr">
         <is>
-          <t>Signup failed: Database error (mock error)</t>
+          <t>Signup successful. New user registered and navigated to dashboard.</t>
         </is>
       </c>
       <c r="G4" s="18" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
       <c r="H4" s="16" t="n">
